--- a/processed/exported.xlsx
+++ b/processed/exported.xlsx
@@ -16056,7 +16056,7 @@
       </c>
       <c r="R201" s="4" t="inlineStr">
         <is>
-          <t>af</t>
+          <t>cy</t>
         </is>
       </c>
     </row>
@@ -43176,7 +43176,7 @@
       </c>
       <c r="R553" s="4" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>tr</t>
         </is>
       </c>
     </row>
@@ -43480,7 +43480,7 @@
       </c>
       <c r="R557" s="4" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>tr</t>
         </is>
       </c>
     </row>
@@ -43556,7 +43556,7 @@
       </c>
       <c r="R558" s="4" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>tr</t>
         </is>
       </c>
     </row>
@@ -43709,7 +43709,7 @@
       </c>
       <c r="R560" s="4" t="inlineStr">
         <is>
-          <t>tr</t>
+          <t>fr</t>
         </is>
       </c>
     </row>
@@ -43937,7 +43937,7 @@
       </c>
       <c r="R563" s="4" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>tr</t>
         </is>
       </c>
     </row>
@@ -44013,7 +44013,7 @@
       </c>
       <c r="R564" s="4" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>tr</t>
         </is>
       </c>
     </row>
@@ -46978,7 +46978,7 @@
       </c>
       <c r="R603" s="4" t="inlineStr">
         <is>
-          <t>af</t>
+          <t>en</t>
         </is>
       </c>
     </row>
@@ -47206,7 +47206,7 @@
       </c>
       <c r="R606" s="4" t="inlineStr">
         <is>
-          <t>af</t>
+          <t>en</t>
         </is>
       </c>
     </row>
@@ -47358,7 +47358,7 @@
       </c>
       <c r="R608" s="4" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>af</t>
         </is>
       </c>
     </row>
@@ -47662,7 +47662,7 @@
       </c>
       <c r="R612" s="4" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>af</t>
         </is>
       </c>
     </row>
@@ -47738,7 +47738,7 @@
       </c>
       <c r="R613" s="4" t="inlineStr">
         <is>
-          <t>af</t>
+          <t>en</t>
         </is>
       </c>
     </row>
@@ -47814,7 +47814,7 @@
       </c>
       <c r="R614" s="4" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>af</t>
         </is>
       </c>
     </row>
@@ -47890,7 +47890,7 @@
       </c>
       <c r="R615" s="4" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>af</t>
         </is>
       </c>
     </row>
@@ -48118,7 +48118,7 @@
       </c>
       <c r="R618" s="4" t="inlineStr">
         <is>
-          <t>af</t>
+          <t>en</t>
         </is>
       </c>
     </row>
@@ -48194,7 +48194,7 @@
       </c>
       <c r="R619" s="4" t="inlineStr">
         <is>
-          <t>af</t>
+          <t>en</t>
         </is>
       </c>
     </row>
